--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_truth(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_truth(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_真结局（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="323">
   <si>
     <t>ID</t>
   </si>
@@ -192,6 +192,9 @@
     <t>37</t>
   </si>
   <si>
+    <t>17 enhanced_suspense-tense-background-music</t>
+  </si>
+  <si>
     <t>源类型=type:exeBC; 层级=11</t>
   </si>
   <si>
@@ -345,7 +348,7 @@
     <t>潺潺的水流声顺着河岸漫了上来，把焚烧建筑带来的热浪冲散了大半。死里逃生的病人们三三两两瘫坐在湿润的河滩上，有人埋着头失声痛哭，望着燃烧的医院方向长久地沉默。</t>
   </si>
   <si>
-    <t>bgfade(sntzm_truth(3)_31,1)</t>
+    <t>bgfade(sntzm_truth(3)_31,1)&amp;unlockscene(scene9)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=27</t>
@@ -357,6 +360,9 @@
     <t>克拉克也来到河边，捧起一掌清泉浇在自己滚烫的脸颊上，像是要洗去皮肤上挥之不去的消毒水和麻药的味道，又似在用河水掩盖眼眶里打转的热泪。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=28</t>
   </si>
   <si>
@@ -414,10 +420,31 @@
     <t>40</t>
   </si>
   <si>
-    <t>达成结局——【罪之焰】</t>
-  </si>
-  <si>
-    <t>shake(screen,1,10,x)&amp;bgfade(sntzm_truth(2)_82,0.8)&amp;bgfade(sntzm_truth(3)_39,1)</t>
+    <r>
+      <t>达成结局</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【罪之焰】</t>
+    </r>
+  </si>
+  <si>
+    <t>11 enhanced the_mountain-hope-background</t>
+  </si>
+  <si>
+    <t>shake(screen,1,10,x)&amp;bgfade(sntzm_truth(2)_82,0.8)&amp;bgfade(sntzm_truth(3)_39,1)&amp;unlockending(Ending4)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=34</t>
@@ -429,7 +456,7 @@
     <t>自那之后的事，多年后回想起来已经有些模糊不清了。记忆里只剩下走廊尽头翻滚的黑烟、克拉克跑过身边时粗重喘息，还有那些因断电而从束缚或催眠中挣脱的病人。</t>
   </si>
   <si>
-    <t>jump(17)</t>
+    <t>jump(18)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=12; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"3","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=17</t>
@@ -2626,7 +2653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" ht="60" spans="1:12">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -2652,7 +2679,7 @@
         <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -2661,12 +2688,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="54" spans="1:12">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -2684,7 +2711,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -2696,15 +2723,15 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="40.5" spans="1:12">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -2722,7 +2749,7 @@
         <v>15</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -2737,12 +2764,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="27" spans="1:12">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -2760,7 +2787,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -2775,12 +2802,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="67.5" spans="1:12">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -2798,7 +2825,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -2813,12 +2840,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" ht="40.5" spans="1:12">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -2836,7 +2863,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -2848,15 +2875,15 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="67.5" spans="1:12">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -2874,7 +2901,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -2889,12 +2916,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:12">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -2912,7 +2939,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -2924,15 +2951,15 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="54" spans="1:12">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -2950,7 +2977,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -2962,15 +2989,15 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" ht="42" spans="1:12">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -2988,7 +3015,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3003,12 +3030,12 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="54" spans="1:12">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3026,7 +3053,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3041,12 +3068,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" ht="40.5" spans="1:12">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3064,7 +3091,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3076,15 +3103,15 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3102,7 +3129,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3117,12 +3144,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:12">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3140,7 +3167,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3152,15 +3179,15 @@
         <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" ht="40.5" spans="1:12">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3178,7 +3205,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3193,12 +3220,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" ht="54" spans="1:12">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3216,7 +3243,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3228,15 +3255,15 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3254,13 +3281,13 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
@@ -3269,12 +3296,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" ht="40.5" spans="1:12">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3292,7 +3319,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3304,15 +3331,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L29" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" ht="42" spans="1:12">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3330,7 +3357,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3345,12 +3372,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" ht="27" spans="1:12">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3368,7 +3395,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3383,12 +3410,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" ht="28.5" spans="1:12">
       <c r="A32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3406,7 +3433,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3421,12 +3448,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3444,7 +3471,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3456,15 +3483,15 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L33" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" ht="30" spans="1:12">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" ht="45" spans="1:12">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3481,28 +3508,28 @@
       <c r="F34" t="s">
         <v>15</v>
       </c>
-      <c r="G34" t="s">
-        <v>126</v>
+      <c r="G34" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L34" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" ht="210" spans="1:12">
       <c r="A35" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3520,7 +3547,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3532,15 +3559,15 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L35" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" ht="210" spans="1:12">
       <c r="A36" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B36" t="s">
         <v>35</v>
@@ -3573,12 +3600,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" ht="40.5" spans="1:12">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3596,7 +3623,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3616,7 +3643,7 @@
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -3634,7 +3661,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -3654,7 +3681,7 @@
     </row>
     <row r="39" ht="54" spans="1:12">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -3672,7 +3699,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -3684,10 +3711,10 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L39" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -3708,47 +3735,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -3756,74 +3783,74 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3845,616 +3872,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C10" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B11" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E11" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F11" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D12" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F13" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B14" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C14" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E14" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D15" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F15" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B16" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C16" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D16" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E16" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F16" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E17" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F17" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C18" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D18" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E18" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F18" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C19" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E19" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C20" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D20" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E20" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F20" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C21" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E21" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F21" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C22" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D22" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E22" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C23" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E23" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F23" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D24" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F24" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E25" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F25" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C26" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E26" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F26" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C27" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D27" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E27" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F27" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s">
+        <v>305</v>
+      </c>
+      <c r="C28" t="s">
+        <v>306</v>
+      </c>
+      <c r="D28" t="s">
         <v>302</v>
       </c>
-      <c r="C28" t="s">
-        <v>303</v>
-      </c>
-      <c r="D28" t="s">
-        <v>299</v>
-      </c>
       <c r="E28" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F28" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C29" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D29" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E29" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F29" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C30" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D30" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E30" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F30" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C31" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D31" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
